--- a/Assets/Resources/Data/Excel/ComItemData.xlsx
+++ b/Assets/Resources/Data/Excel/ComItemData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26327"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26501"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\github\grunge\Assets\Resources\Data\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23EBB7D1-822E-4E65-8257-A5E784621D44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4210913E-E750-4633-B77B-D8ACB8E3A688}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" xr2:uid="{C1A8997D-9192-4158-B3C1-2C28844A3146}"/>
+    <workbookView xWindow="-28920" yWindow="11385" windowWidth="29040" windowHeight="15840" xr2:uid="{C1A8997D-9192-4158-B3C1-2C28844A3146}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
